--- a/members/P2_Form_BP_Cong_Nghe - Dinh Tien Chuong.xlsx
+++ b/members/P2_Form_BP_Cong_Nghe - Dinh Tien Chuong.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CONG VIEC\project-management\members\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FCD00F4-3784-467A-895C-4C432C3962ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77EEDDCF-C482-4064-BC0F-DD765144554F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,136 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="153">
+  <si>
+    <t>P2 PERFORMANCE EVALUATION – Product Engineer</t>
+  </si>
+  <si>
+    <t>Họ và tên</t>
+  </si>
+  <si>
+    <t>Bùi Văn Hổ</t>
+  </si>
+  <si>
+    <t>Kỳ đánh giá</t>
+  </si>
+  <si>
+    <t>Vai trò</t>
+  </si>
+  <si>
+    <t>Người đánh giá</t>
+  </si>
+  <si>
+    <t>Nhóm năng lực</t>
+  </si>
+  <si>
+    <t>Trọng số (%)</t>
+  </si>
+  <si>
+    <t>Mức (L0/L1/L2/L3)</t>
+  </si>
+  <si>
+    <t>Điểm quy đổi</t>
+  </si>
+  <si>
+    <t>Nhận xét</t>
+  </si>
+  <si>
+    <t>A. Năng lực kỹ thuật</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>B. Ownership &amp; trách nhiệm</t>
+  </si>
+  <si>
+    <t>C. DevOps &amp; vận hành (bắt buộc)</t>
+  </si>
+  <si>
+    <t>cần thực hành thêm</t>
+  </si>
+  <si>
+    <t>D. AI Agent &amp; cải tiến (bắt buộc)</t>
+  </si>
+  <si>
+    <t>TỔNG P2</t>
+  </si>
+  <si>
+    <t>THANG ĐÁNH GIÁ CHI TIẾT (L0/L1/L2/L3)</t>
+  </si>
+  <si>
+    <t>Mức</t>
+  </si>
+  <si>
+    <t>Mô tả</t>
+  </si>
+  <si>
+    <t>L0</t>
+  </si>
+  <si>
+    <t>Chưa đạt kết quả hoặc năng lực chưa đạt.</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>Thực hiện được các phần việc rõ ràng khi có hướng dẫn; cần review thường xuyên; chất lượng chưa ổn định.</t>
+  </si>
+  <si>
+    <t>Tự triển khai độc lập; chất lượng ổn định, ít rework; chủ động xử lý rủi ro và cải thiện sản phẩm.</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <t>Extra: Không chỉ hoàn thành tốt phần việc cá nhân mà còn cải tiến hệ thống, chuẩn hoá cách làm và lan toả kinh nghiệm cho nhóm.</t>
+  </si>
+  <si>
+    <t>Kết quả công việc (P2-Delivery – từ OKR/KPI)</t>
+  </si>
+  <si>
+    <t>Phần này phản ánh kết quả đầu ra, không đánh giá lại năng lực hay cách làm việc. (P2-Core là phần đánh giá NĂNG LỰC &amp; CÁCH LÀM VIỆC mang tính nền tảng và dài hạn của nhân sự Công Nghệ.)</t>
+  </si>
+  <si>
+    <t>Tiêu chí</t>
+  </si>
+  <si>
+    <t>Điểm (Chưa đạt &lt; 1, Đạt &gt;=1, Tốt=1.2)</t>
+  </si>
+  <si>
+    <t>Mức độ hoàn thành OKR</t>
+  </si>
+  <si>
+    <t>Tỷ lệ hoàn thành các mục tiêu đã cam kết trong kỳ đánh giá</t>
+  </si>
+  <si>
+    <t>Chưa đạt</t>
+  </si>
+  <si>
+    <t>Chất lượng kết quả</t>
+  </si>
+  <si>
+    <t>Ít lỗi nghiêm trọng; hạn chế làm lại; không gây rủi ro hệ thống</t>
+  </si>
+  <si>
+    <t>Cam kết &amp; tiến độ</t>
+  </si>
+  <si>
+    <t>Hoàn thành đúng hạn; chủ động báo sớm rủi ro; phối hợp tốt</t>
+  </si>
+  <si>
+    <t>Tốt</t>
+  </si>
+  <si>
+    <t>P2-Delivery = Trung bình cộng các tiêu chí trên</t>
+  </si>
+  <si>
+    <t>P2-Delivery</t>
+  </si>
+  <si>
+    <t>P2+ Tổng</t>
+  </si>
   <si>
     <t>P2+ - MÔ HÌNH ĐÁNH GIÁ NĂNG LỰC MỞ RỘNG</t>
   </si>
@@ -137,367 +266,238 @@
     <t>IV. NGƯỠNG XẾP LOẠI</t>
   </si>
   <si>
-    <t>P2+ Tổng</t>
-  </si>
-  <si>
     <t>Xếp loại</t>
   </si>
   <si>
-    <t>&lt; 2.8</t>
-  </si>
-  <si>
-    <t>Chưa đạt</t>
-  </si>
-  <si>
-    <t>2.8 – 3.4</t>
+    <t>&lt; 1</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>Đạt</t>
   </si>
   <si>
-    <t>3.5 – 4.1</t>
-  </si>
-  <si>
-    <t>Tốt</t>
-  </si>
-  <si>
-    <t>≥ 4.2</t>
-  </si>
-  <si>
-    <t>Xuất sắc</t>
-  </si>
-  <si>
-    <t>P2 PERFORMANCE EVALUATION – Product Engineer</t>
-  </si>
-  <si>
-    <t>Họ và tên</t>
+    <t>&gt; 1 và ≤ 1.2</t>
+  </si>
+  <si>
+    <t>MÔ TẢ NĂNG LỰC THEO VAI TRÒ</t>
+  </si>
+  <si>
+    <t>Gợi ý: dùng nút +/- (Outline) để thu gọn/mở rộng theo từng Vai trò. Cấp độ 1 (Thực thi – phối hợp): Làm tốt phần việc kỹ thuật của mình | Cấp độ 2 (Chủ động – cải tiến): Giải quyết bài toán xuyên hệ thống | Cấp độ 3 (Chuẩn hoá – dẫn dắt): Định hướng, tạo chuẩn, mở rộng</t>
+  </si>
+  <si>
+    <t>Backend</t>
+  </si>
+  <si>
+    <t>Cấp độ 1</t>
+  </si>
+  <si>
+    <t>Cấp độ 2</t>
+  </si>
+  <si>
+    <t>Cấp độ 3</t>
+  </si>
+  <si>
+    <t>Tự triển khai tính năng (API + DB); code dễ đọc; tests cơ bản; xử lý trường hợp lỗi không mong muốn xảy ra.</t>
+  </si>
+  <si>
+    <t>Thiết kế kiến trúc/module gọn; cải thiện performance/security; tests chắc; nâng chất lượng qua review.</t>
+  </si>
+  <si>
+    <t>Định hướng kiến trúc hệ thống có khả năng mở rộng; chủ động ngăn ngừa rủi ro và lỗi hệ thống; dẫn dắt cải tiến kỹ thuật lớn và hỗ trợ nâng cao năng lực đội ngũ.</t>
+  </si>
+  <si>
+    <t>Bàn giao công việc ổn định; biết tách công việc thành các đầu việc rõ ràng; chịu trách nhiệm xử lý lỗi đến khi hoàn tất; chủ động báo sớm các rủi ro phát sinh.</t>
+  </si>
+  <si>
+    <t>Chủ động quản lý phạm vi và rủi ro công việc; phối hợp hiệu quả với các bộ phận liên quan; giảm phát sinh làm lại nhờ yêu cầu và tài liệu được chuẩn bị rõ ràng.</t>
+  </si>
+  <si>
+    <t>Cải tiến quy trình bàn giao công việc trong đội (tiêu chí hoàn thành, danh sách rà soát); xử lý các điểm nghẽn trong phối hợp giữa các nhóm; nâng cao khả năng dự báo và kiểm soát tiến độ chung.</t>
+  </si>
+  <si>
+    <t>C. DevOps &amp; vận hành</t>
+  </si>
+  <si>
+    <t>Thực hiện quy trình tích hợp và triển khai tự động; hiểu và sử dụng đúng cấu hình môi trường, thông tin bảo mật; theo dõi nhật ký và lỗi hệ thống; tham gia trực xử lý sự cố khi cần.</t>
+  </si>
+  <si>
+    <t>Chủ động cải thiện quy trình triển khai (tối ưu hiệu năng, kiểm soát chất lượng); bổ sung theo dõi chỉ số và cảnh báo; thực hiện phương án quay lui khi có sự cố; nâng cao độ ổn định và rút ngắn thời gian khắc phục lỗi.</t>
+  </si>
+  <si>
+    <t>Chuẩn hóa quy trình phát hành và giám sát hệ thống; xây dựng hướng dẫn vận hành và xử lý sự cố; chủ trì phân tích nguyên nhân sau sự cố; hướng dẫn và nâng cao năng lực vận hành cho đội ngũ.</t>
+  </si>
+  <si>
+    <t>D. AI Agent &amp; cải tiến</t>
+  </si>
+  <si>
+    <t>Sử dụng AI Agent để hỗ trợ code, chỉnh sửa code, viết kiểm thử và tìm lỗi; biết đặt yêu cầu rõ ràng; luôn kiểm tra lại kết quả trước khi áp dụng.</t>
+  </si>
+  <si>
+    <t>Xây dựng mẫu yêu cầu và quy trình làm việc có thể tái sử dụng; dùng AI để hỗ trợ rà soát và tìm lỗi; theo dõi hiệu quả bằng các chỉ số như thời gian hoàn thành và tỷ lệ lỗi phát sinh.</t>
+  </si>
+  <si>
+    <t>Dẫn dắt việc áp dụng AI trong kỹ thuật một cách có kiểm soát; đào tạo và hướng dẫn đội ngũ; tự động hóa các công việc lặp lại theo nguyên tắc an toàn, phân quyền và tuân thủ quy định nội bộ.</t>
+  </si>
+  <si>
+    <t>Designer</t>
+  </si>
+  <si>
+    <t>Tự xây dựng luồng trải nghiệm và đặc tả giao diện; đảm bảo tính nhất quán về hình ảnh; bàn giao thiết kế rõ ràng để đội triển khai chính xác.</t>
+  </si>
+  <si>
+    <t>Cải thiện khả năng sử dụng dựa trên nghiên cứu và đánh giá trải nghiệm; phát triển và mở rộng hệ thống thiết kế; giảm phát sinh làm lại nhờ đặc tả thiết kế rõ ràng.</t>
+  </si>
+  <si>
+    <t>Định hướng thiết kế tổng thể; tạo ra tác động trải nghiệm người dùng có thể đo lường; quản trị và chuẩn hóa hệ thống thiết kế; hướng dẫn và kết nối các đội cùng áp dụng.</t>
+  </si>
+  <si>
+    <t>Bàn giao công việc ổn định; xác định rõ phạm vi; lặp lại thiết kế kịp thời; phối hợp sớm với các bên triển khai để thống nhất ràng buộc.</t>
+  </si>
+  <si>
+    <t>Quản lý các lựa chọn và đánh đổi trong thiết kế; chuẩn bị phương án thay thế; ghi nhận rõ các quyết định; giảm phát sinh làm lại thông qua rà soát thiết kế.</t>
+  </si>
+  <si>
+    <t>Nâng chuẩn bàn giao thiết kế (tiêu chí hoàn thành, danh sách rà soát); tháo gỡ các vướng mắc phối hợp giữa các đội; nâng cao khả năng dự báo và kiểm soát tiến độ.</t>
+  </si>
+  <si>
+    <t>Làm việc với môi trường preview và staging; sử dụng nhất quán các thành phần và chuẩn thiết kế; xây dựng đặc tả phù hợp với khả năng triển khai.</t>
+  </si>
+  <si>
+    <t>Thúc đẩy áp dụng chuẩn thành phần thiết kế; cải thiện tự động hóa bàn giao thiết kế–triển khai; giảm lỗi tích hợp và công việc làm lại.</t>
+  </si>
+  <si>
+    <t>Dẫn dắt chuẩn hóa quy trình thiết kế–triển khai với đội phát triển; xây dựng hướng dẫn và các thực hành tốt cho toàn đội.</t>
+  </si>
+  <si>
+    <t>Sử dụng AI để hỗ trợ xây dựng khung thiết kế, nội dung trải nghiệm và phương án thiết kế; biết đặt yêu cầu phù hợp; kiểm tra và đối chiếu với hệ thống thiết kế hiện có.</t>
+  </si>
+  <si>
+    <t>Xây dựng thư viện yêu cầu AI có thể tái sử dụng; tăng tốc tổng hợp nghiên cứu; theo dõi tác động của AI đến thời gian thực hiện và mức độ làm lại.</t>
+  </si>
+  <si>
+    <t>Dẫn dắt việc áp dụng AI trong thiết kế một cách an toàn và có kiểm soát; đào tạo đội ngũ; tự động hóa các công việc lặp lại theo quy định và chuẩn quản trị.</t>
+  </si>
+  <si>
+    <t>FrontEnd</t>
+  </si>
+  <si>
+    <t>Tự triển khai tính năng giao diện từ đầu đến cuối (giao diện, trạng thái, tích hợp dữ liệu); xử lý các tình huống phát sinh; viết mã rõ ràng, dễ bảo trì.</t>
+  </si>
+  <si>
+    <t>Cải thiện hiệu năng và khả năng truy cập của giao diện; xây dựng thành phần dùng lại; nâng cao kiến trúc và kiểm thử để tăng độ ổn định.</t>
+  </si>
+  <si>
+    <t>Định hướng kỹ thuật frontend; dẫn dắt các thay đổi lớn để giảm rủi ro; hướng dẫn đội ngũ; chủ động ngăn ngừa lỗi ảnh hưởng diện rộng trên giao diện.</t>
+  </si>
+  <si>
+    <t>Bàn giao công việc ổn định; chịu trách nhiệm xử lý lỗi đến khi hoàn tất; phối hợp sớm với backend và thiết kế; chủ động báo rủi ro.</t>
+  </si>
+  <si>
+    <t>Quản lý các lựa chọn và đánh đổi về trải nghiệm người dùng; giảm phát sinh làm lại; nâng chất lượng bàn giao bằng đặc tả, minh chứng và tài liệu rõ ràng.</t>
+  </si>
+  <si>
+    <t>Nâng chuẩn bàn giao và rà soát (chuẩn thành phần, danh sách rà soát); tháo gỡ vướng mắc phối hợp giữa các đội; nâng cao khả năng dự báo và kiểm soát tiến độ.</t>
+  </si>
+  <si>
+    <t>Sử dụng thành thạo quy trình tích hợp và triển khai; quản lý cấu hình môi trường; theo dõi lỗi phía người dùng; giữ bản phát hành gọn và ổn định.</t>
+  </si>
+  <si>
+    <t>Cải thiện quy trình triển khai (tối ưu tốc độ, kiểm soát chất lượng); giảm kích thước và thời gian tải; có phương án quay lui khi sự cố; nâng cao độ ổn định.</t>
+  </si>
+  <si>
+    <t>Chuẩn hóa phát hành và giám sát cho frontend; xây dựng hướng dẫn xử lý sự cố; hướng dẫn đội ngũ thực hành vận hành; giảm lỗi phía người dùng và rút ngắn thời gian khắc phục.</t>
+  </si>
+  <si>
+    <t>Sử dụng AI để hỗ trợ tạo khung code, chỉnh sửa code, viết kiểm thử và tìm lỗi; biết đặt yêu cầu rõ ràng; luôn kiểm tra lại trước khi áp dụng.</t>
+  </si>
+  <si>
+    <t>Xây dựng mẫu yêu cầu AI có thể tái sử dụng (thành phần, khả năng truy cập, kiểm thử); dùng AI hỗ trợ rà soát và cải tiến mã; theo dõi hiệu quả bằng các chỉ số phù hợp.</t>
+  </si>
+  <si>
+    <t>Dẫn dắt việc áp dụng AI trong frontend theo quy chuẩn; đào tạo đội ngũ; tự động hóa các công việc lặp lại một cách an toàn và có kiểm soát.</t>
+  </si>
+  <si>
+    <t>FullStack</t>
+  </si>
+  <si>
+    <t>Tự triển khai tính năng từ đầu đến cuối (giao diện, xử lý dữ liệu, lưu trữ); đảm bảo chất lượng cơ bản; viết kiểm thử cần thiết; xử lý các tình huống lỗi phát sinh.</t>
+  </si>
+  <si>
+    <t>Phân định rõ trách nhiệm giữa backend và frontend; cải thiện hiệu năng và an toàn hệ thống; thực hiện tái cấu trúc có kiểm soát; xây dựng kiểm thử vững chắc hơn.</t>
+  </si>
+  <si>
+    <t>Định hướng kỹ thuật end-to-end; chủ động ngăn ngừa rủi ro và lỗi hệ thống; hướng dẫn đội ngũ; dẫn dắt các đợt tái cấu trúc và chuyển đổi hệ thống lớn một cách an toàn.</t>
+  </si>
+  <si>
+    <t>Chịu trách nhiệm toàn bộ tính năng từ đầu đến cuối; đảm bảo vận hành ổn định; chủ động báo rủi ro; xử lý triệt để vấn đề đến khi hoàn tất.</t>
+  </si>
+  <si>
+    <t>Quản lý phạm vi và rủi ro công việc; trao đổi và thống nhất các đánh đổi kỹ thuật; giảm phát sinh làm lại; cải thiện chất lượng tài liệu và bàn giao.</t>
+  </si>
+  <si>
+    <t>Nâng cao khả năng dự báo; xây dựng và áp dụng các chuẩn chung (tiêu chí hoàn thành, danh sách rà soát); tháo gỡ vướng mắc trong phối hợp giữa các đội.</t>
+  </si>
+  <si>
+    <t>Sử dụng quy trình tích hợp và triển khai tự động; quản lý cấu hình và thông tin bảo mật; theo dõi lỗi và nhật ký hệ thống; triển khai an toàn và tham gia trực xử lý sự cố.</t>
+  </si>
+  <si>
+    <t>Cải thiện quy trình triển khai; bổ sung theo dõi chỉ số và cảnh báo; có phương án quay lui khi cần; nâng cao độ ổn định trên toàn bộ hệ thống.</t>
+  </si>
+  <si>
+    <t>Chuẩn hóa phát hành và giám sát hệ thống; xây dựng hướng dẫn vận hành và xử lý sự cố; giảm thời gian khắc phục lỗi; hướng dẫn đội ngũ thực hành vận hành hiệu quả.</t>
+  </si>
+  <si>
+    <t>Sử dụng AI hỗ trợ toàn bộ chuỗi phát triển (tạo khung, chỉnh sửa code, kiểm thử, tìm lỗi); biết đặt yêu cầu phù hợp; luôn rà soát kỹ kết quả trước khi áp dụng.</t>
+  </si>
+  <si>
+    <t>Xây dựng mẫu yêu cầu và quy trình làm việc với AI có thể tái sử dụng; dùng AI hỗ trợ rà soát và tìm lỗi; theo dõi tác động đến thời gian thực hiện và chất lượng.</t>
+  </si>
+  <si>
+    <t>Dẫn dắt việc áp dụng AI trong phát triển end-to-end một cách an toàn và có kiểm soát; đào tạo đội ngũ; tự động hóa các công việc xuyên suốt theo chuẩn quản trị.</t>
+  </si>
+  <si>
+    <t>P2 SUMMARY &amp; RANKING – BP CÔNG NGHỆ</t>
+  </si>
+  <si>
+    <t>Nhập dữ liệu đánh giá của nhiều nhân sự để tự động xếp hạng. Cột 'Điểm P2' có thể nhập tay hoặc liên kết từ sheet role.</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Điểm P2</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>P2-Core</t>
+  </si>
+  <si>
+    <t>OKR (P2-Delivery)</t>
+  </si>
+  <si>
+    <t>Designer, Frontend</t>
+  </si>
+  <si>
+    <t>Nguyễn Huy Hoàng</t>
+  </si>
+  <si>
+    <t>Backend, Frontend</t>
   </si>
   <si>
     <t>Đinh Tiến Chương</t>
   </si>
   <si>
-    <t>Kỳ đánh giá</t>
-  </si>
-  <si>
-    <t>Vai trò</t>
+    <t>Nguyễn Đăng Đức</t>
   </si>
   <si>
     <t>Frontend</t>
-  </si>
-  <si>
-    <t>Người đánh giá</t>
-  </si>
-  <si>
-    <t>Nhóm năng lực</t>
-  </si>
-  <si>
-    <t>Trọng số (%)</t>
-  </si>
-  <si>
-    <t>Mức (L1/L2/L3)</t>
-  </si>
-  <si>
-    <t>Điểm quy đổi</t>
-  </si>
-  <si>
-    <t>Nhận xét</t>
-  </si>
-  <si>
-    <t>A. Năng lực kỹ thuật</t>
-  </si>
-  <si>
-    <t>L2</t>
-  </si>
-  <si>
-    <t>B. Ownership &amp; trách nhiệm</t>
-  </si>
-  <si>
-    <t>C. DevOps &amp; vận hành (bắt buộc)</t>
-  </si>
-  <si>
-    <t>cần thực hành thêm</t>
-  </si>
-  <si>
-    <t>D. AI Agent &amp; cải tiến (bắt buộc)</t>
-  </si>
-  <si>
-    <t>TỔNG P2</t>
-  </si>
-  <si>
-    <t>THANG ĐÁNH GIÁ CHI TIẾT (L1/L2/L3)</t>
-  </si>
-  <si>
-    <t>Mức</t>
-  </si>
-  <si>
-    <t>Mô tả</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>Thực hiện được các phần việc rõ ràng khi có hướng dẫn; cần review thường xuyên; chất lượng chưa ổn định.</t>
-  </si>
-  <si>
-    <t>Tự triển khai độc lập; chất lượng ổn định, ít rework; chủ động xử lý rủi ro và cải thiện sản phẩm.</t>
-  </si>
-  <si>
-    <t>L3</t>
-  </si>
-  <si>
-    <t>Extra: Không chỉ hoàn thành tốt phần việc cá nhân mà còn cải tiến hệ thống, chuẩn hoá cách làm và lan toả kinh nghiệm cho nhóm.</t>
-  </si>
-  <si>
-    <t>Kết quả công việc (P2-Delivery – từ OKR/KPI)</t>
-  </si>
-  <si>
-    <t>Phần này phản ánh kết quả đầu ra, không đánh giá lại năng lực hay cách làm việc. (P2-Core là phần đánh giá NĂNG LỰC &amp; CÁCH LÀM VIỆC mang tính nền tảng và dài hạn của nhân sự Công Nghệ.)</t>
-  </si>
-  <si>
-    <t>Tiêu chí</t>
-  </si>
-  <si>
-    <t>Điểm (Chưa đạt=1.5, Đạt=3.5, Tốt=5)</t>
-  </si>
-  <si>
-    <t>Mức độ hoàn thành OKR</t>
-  </si>
-  <si>
-    <t>Tỷ lệ hoàn thành các mục tiêu đã cam kết trong kỳ đánh giá</t>
-  </si>
-  <si>
-    <t>Chất lượng kết quả</t>
-  </si>
-  <si>
-    <t>Ít lỗi nghiêm trọng; hạn chế làm lại; không gây rủi ro hệ thống</t>
-  </si>
-  <si>
-    <t>Cam kết &amp; tiến độ</t>
-  </si>
-  <si>
-    <t>Hoàn thành đúng hạn; chủ động báo sớm rủi ro; phối hợp tốt</t>
-  </si>
-  <si>
-    <t>P2-Delivery = Trung bình cộng các tiêu chí trên</t>
-  </si>
-  <si>
-    <t>P2-Delivery</t>
-  </si>
-  <si>
-    <t>MÔ TẢ NĂNG LỰC THEO VAI TRÒ</t>
-  </si>
-  <si>
-    <t>Gợi ý: dùng nút +/- (Outline) để thu gọn/mở rộng theo từng Vai trò. Cấp độ 1 (Thực thi – phối hợp): Làm tốt phần việc kỹ thuật của mình | Cấp độ 2 (Chủ động – cải tiến): Giải quyết bài toán xuyên hệ thống | Cấp độ 3 (Chuẩn hoá – dẫn dắt): Định hướng, tạo chuẩn, mở rộng</t>
-  </si>
-  <si>
-    <t>Backend</t>
-  </si>
-  <si>
-    <t>Cấp độ 1</t>
-  </si>
-  <si>
-    <t>Cấp độ 2</t>
-  </si>
-  <si>
-    <t>Cấp độ 3</t>
-  </si>
-  <si>
-    <t>Tự triển khai tính năng (API + DB); code dễ đọc; tests cơ bản; xử lý trường hợp lỗi không mong muốn xảy ra.</t>
-  </si>
-  <si>
-    <t>Thiết kế kiến trúc/module gọn; cải thiện performance/security; tests chắc; nâng chất lượng qua review.</t>
-  </si>
-  <si>
-    <t>Định hướng kiến trúc hệ thống có khả năng mở rộng; chủ động ngăn ngừa rủi ro và lỗi hệ thống; dẫn dắt cải tiến kỹ thuật lớn và hỗ trợ nâng cao năng lực đội ngũ.</t>
-  </si>
-  <si>
-    <t>Bàn giao công việc ổn định; biết tách công việc thành các đầu việc rõ ràng; chịu trách nhiệm xử lý lỗi đến khi hoàn tất; chủ động báo sớm các rủi ro phát sinh.</t>
-  </si>
-  <si>
-    <t>Chủ động quản lý phạm vi và rủi ro công việc; phối hợp hiệu quả với các bộ phận liên quan; giảm phát sinh làm lại nhờ yêu cầu và tài liệu được chuẩn bị rõ ràng.</t>
-  </si>
-  <si>
-    <t>Cải tiến quy trình bàn giao công việc trong đội (tiêu chí hoàn thành, danh sách rà soát); xử lý các điểm nghẽn trong phối hợp giữa các nhóm; nâng cao khả năng dự báo và kiểm soát tiến độ chung.</t>
-  </si>
-  <si>
-    <t>C. DevOps &amp; vận hành</t>
-  </si>
-  <si>
-    <t>Thực hiện quy trình tích hợp và triển khai tự động; hiểu và sử dụng đúng cấu hình môi trường, thông tin bảo mật; theo dõi nhật ký và lỗi hệ thống; tham gia trực xử lý sự cố khi cần.</t>
-  </si>
-  <si>
-    <t>Chủ động cải thiện quy trình triển khai (tối ưu hiệu năng, kiểm soát chất lượng); bổ sung theo dõi chỉ số và cảnh báo; thực hiện phương án quay lui khi có sự cố; nâng cao độ ổn định và rút ngắn thời gian khắc phục lỗi.</t>
-  </si>
-  <si>
-    <t>Chuẩn hóa quy trình phát hành và giám sát hệ thống; xây dựng hướng dẫn vận hành và xử lý sự cố; chủ trì phân tích nguyên nhân sau sự cố; hướng dẫn và nâng cao năng lực vận hành cho đội ngũ.</t>
-  </si>
-  <si>
-    <t>D. AI Agent &amp; cải tiến</t>
-  </si>
-  <si>
-    <t>Sử dụng AI Agent để hỗ trợ code, chỉnh sửa code, viết kiểm thử và tìm lỗi; biết đặt yêu cầu rõ ràng; luôn kiểm tra lại kết quả trước khi áp dụng.</t>
-  </si>
-  <si>
-    <t>Xây dựng mẫu yêu cầu và quy trình làm việc có thể tái sử dụng; dùng AI để hỗ trợ rà soát và tìm lỗi; theo dõi hiệu quả bằng các chỉ số như thời gian hoàn thành và tỷ lệ lỗi phát sinh.</t>
-  </si>
-  <si>
-    <t>Dẫn dắt việc áp dụng AI trong kỹ thuật một cách có kiểm soát; đào tạo và hướng dẫn đội ngũ; tự động hóa các công việc lặp lại theo nguyên tắc an toàn, phân quyền và tuân thủ quy định nội bộ.</t>
-  </si>
-  <si>
-    <t>Designer</t>
-  </si>
-  <si>
-    <t>Tự xây dựng luồng trải nghiệm và đặc tả giao diện; đảm bảo tính nhất quán về hình ảnh; bàn giao thiết kế rõ ràng để đội triển khai chính xác.</t>
-  </si>
-  <si>
-    <t>Cải thiện khả năng sử dụng dựa trên nghiên cứu và đánh giá trải nghiệm; phát triển và mở rộng hệ thống thiết kế; giảm phát sinh làm lại nhờ đặc tả thiết kế rõ ràng.</t>
-  </si>
-  <si>
-    <t>Định hướng thiết kế tổng thể; tạo ra tác động trải nghiệm người dùng có thể đo lường; quản trị và chuẩn hóa hệ thống thiết kế; hướng dẫn và kết nối các đội cùng áp dụng.</t>
-  </si>
-  <si>
-    <t>Bàn giao công việc ổn định; xác định rõ phạm vi; lặp lại thiết kế kịp thời; phối hợp sớm với các bên triển khai để thống nhất ràng buộc.</t>
-  </si>
-  <si>
-    <t>Quản lý các lựa chọn và đánh đổi trong thiết kế; chuẩn bị phương án thay thế; ghi nhận rõ các quyết định; giảm phát sinh làm lại thông qua rà soát thiết kế.</t>
-  </si>
-  <si>
-    <t>Nâng chuẩn bàn giao thiết kế (tiêu chí hoàn thành, danh sách rà soát); tháo gỡ các vướng mắc phối hợp giữa các đội; nâng cao khả năng dự báo và kiểm soát tiến độ.</t>
-  </si>
-  <si>
-    <t>Làm việc với môi trường preview và staging; sử dụng nhất quán các thành phần và chuẩn thiết kế; xây dựng đặc tả phù hợp với khả năng triển khai.</t>
-  </si>
-  <si>
-    <t>Thúc đẩy áp dụng chuẩn thành phần thiết kế; cải thiện tự động hóa bàn giao thiết kế–triển khai; giảm lỗi tích hợp và công việc làm lại.</t>
-  </si>
-  <si>
-    <t>Dẫn dắt chuẩn hóa quy trình thiết kế–triển khai với đội phát triển; xây dựng hướng dẫn và các thực hành tốt cho toàn đội.</t>
-  </si>
-  <si>
-    <t>Sử dụng AI để hỗ trợ xây dựng khung thiết kế, nội dung trải nghiệm và phương án thiết kế; biết đặt yêu cầu phù hợp; kiểm tra và đối chiếu với hệ thống thiết kế hiện có.</t>
-  </si>
-  <si>
-    <t>Xây dựng thư viện yêu cầu AI có thể tái sử dụng; tăng tốc tổng hợp nghiên cứu; theo dõi tác động của AI đến thời gian thực hiện và mức độ làm lại.</t>
-  </si>
-  <si>
-    <t>Dẫn dắt việc áp dụng AI trong thiết kế một cách an toàn và có kiểm soát; đào tạo đội ngũ; tự động hóa các công việc lặp lại theo quy định và chuẩn quản trị.</t>
-  </si>
-  <si>
-    <t>FrontEnd</t>
-  </si>
-  <si>
-    <t>Tự triển khai tính năng giao diện từ đầu đến cuối (giao diện, trạng thái, tích hợp dữ liệu); xử lý các tình huống phát sinh; viết mã rõ ràng, dễ bảo trì.</t>
-  </si>
-  <si>
-    <t>Cải thiện hiệu năng và khả năng truy cập của giao diện; xây dựng thành phần dùng lại; nâng cao kiến trúc và kiểm thử để tăng độ ổn định.</t>
-  </si>
-  <si>
-    <t>Định hướng kỹ thuật frontend; dẫn dắt các thay đổi lớn để giảm rủi ro; hướng dẫn đội ngũ; chủ động ngăn ngừa lỗi ảnh hưởng diện rộng trên giao diện.</t>
-  </si>
-  <si>
-    <t>Bàn giao công việc ổn định; chịu trách nhiệm xử lý lỗi đến khi hoàn tất; phối hợp sớm với backend và thiết kế; chủ động báo rủi ro.</t>
-  </si>
-  <si>
-    <t>Quản lý các lựa chọn và đánh đổi về trải nghiệm người dùng; giảm phát sinh làm lại; nâng chất lượng bàn giao bằng đặc tả, minh chứng và tài liệu rõ ràng.</t>
-  </si>
-  <si>
-    <t>Nâng chuẩn bàn giao và rà soát (chuẩn thành phần, danh sách rà soát); tháo gỡ vướng mắc phối hợp giữa các đội; nâng cao khả năng dự báo và kiểm soát tiến độ.</t>
-  </si>
-  <si>
-    <t>Sử dụng thành thạo quy trình tích hợp và triển khai; quản lý cấu hình môi trường; theo dõi lỗi phía người dùng; giữ bản phát hành gọn và ổn định.</t>
-  </si>
-  <si>
-    <t>Cải thiện quy trình triển khai (tối ưu tốc độ, kiểm soát chất lượng); giảm kích thước và thời gian tải; có phương án quay lui khi sự cố; nâng cao độ ổn định.</t>
-  </si>
-  <si>
-    <t>Chuẩn hóa phát hành và giám sát cho frontend; xây dựng hướng dẫn xử lý sự cố; hướng dẫn đội ngũ thực hành vận hành; giảm lỗi phía người dùng và rút ngắn thời gian khắc phục.</t>
-  </si>
-  <si>
-    <t>Sử dụng AI để hỗ trợ tạo khung code, chỉnh sửa code, viết kiểm thử và tìm lỗi; biết đặt yêu cầu rõ ràng; luôn kiểm tra lại trước khi áp dụng.</t>
-  </si>
-  <si>
-    <t>Xây dựng mẫu yêu cầu AI có thể tái sử dụng (thành phần, khả năng truy cập, kiểm thử); dùng AI hỗ trợ rà soát và cải tiến mã; theo dõi hiệu quả bằng các chỉ số phù hợp.</t>
-  </si>
-  <si>
-    <t>Dẫn dắt việc áp dụng AI trong frontend theo quy chuẩn; đào tạo đội ngũ; tự động hóa các công việc lặp lại một cách an toàn và có kiểm soát.</t>
-  </si>
-  <si>
-    <t>FullStack</t>
-  </si>
-  <si>
-    <t>Tự triển khai tính năng từ đầu đến cuối (giao diện, xử lý dữ liệu, lưu trữ); đảm bảo chất lượng cơ bản; viết kiểm thử cần thiết; xử lý các tình huống lỗi phát sinh.</t>
-  </si>
-  <si>
-    <t>Phân định rõ trách nhiệm giữa backend và frontend; cải thiện hiệu năng và an toàn hệ thống; thực hiện tái cấu trúc có kiểm soát; xây dựng kiểm thử vững chắc hơn.</t>
-  </si>
-  <si>
-    <t>Định hướng kỹ thuật end-to-end; chủ động ngăn ngừa rủi ro và lỗi hệ thống; hướng dẫn đội ngũ; dẫn dắt các đợt tái cấu trúc và chuyển đổi hệ thống lớn một cách an toàn.</t>
-  </si>
-  <si>
-    <t>Chịu trách nhiệm toàn bộ tính năng từ đầu đến cuối; đảm bảo vận hành ổn định; chủ động báo rủi ro; xử lý triệt để vấn đề đến khi hoàn tất.</t>
-  </si>
-  <si>
-    <t>Quản lý phạm vi và rủi ro công việc; trao đổi và thống nhất các đánh đổi kỹ thuật; giảm phát sinh làm lại; cải thiện chất lượng tài liệu và bàn giao.</t>
-  </si>
-  <si>
-    <t>Nâng cao khả năng dự báo; xây dựng và áp dụng các chuẩn chung (tiêu chí hoàn thành, danh sách rà soát); tháo gỡ vướng mắc trong phối hợp giữa các đội.</t>
-  </si>
-  <si>
-    <t>Sử dụng quy trình tích hợp và triển khai tự động; quản lý cấu hình và thông tin bảo mật; theo dõi lỗi và nhật ký hệ thống; triển khai an toàn và tham gia trực xử lý sự cố.</t>
-  </si>
-  <si>
-    <t>Cải thiện quy trình triển khai; bổ sung theo dõi chỉ số và cảnh báo; có phương án quay lui khi cần; nâng cao độ ổn định trên toàn bộ hệ thống.</t>
-  </si>
-  <si>
-    <t>Chuẩn hóa phát hành và giám sát hệ thống; xây dựng hướng dẫn vận hành và xử lý sự cố; giảm thời gian khắc phục lỗi; hướng dẫn đội ngũ thực hành vận hành hiệu quả.</t>
-  </si>
-  <si>
-    <t>Sử dụng AI hỗ trợ toàn bộ chuỗi phát triển (tạo khung, chỉnh sửa code, kiểm thử, tìm lỗi); biết đặt yêu cầu phù hợp; luôn rà soát kỹ kết quả trước khi áp dụng.</t>
-  </si>
-  <si>
-    <t>Xây dựng mẫu yêu cầu và quy trình làm việc với AI có thể tái sử dụng; dùng AI hỗ trợ rà soát và tìm lỗi; theo dõi tác động đến thời gian thực hiện và chất lượng.</t>
-  </si>
-  <si>
-    <t>Dẫn dắt việc áp dụng AI trong phát triển end-to-end một cách an toàn và có kiểm soát; đào tạo đội ngũ; tự động hóa các công việc xuyên suốt theo chuẩn quản trị.</t>
-  </si>
-  <si>
-    <t>P2 SUMMARY &amp; RANKING – BP CÔNG NGHỆ</t>
-  </si>
-  <si>
-    <t>Nhập dữ liệu đánh giá của nhiều nhân sự để tự động xếp hạng. Cột 'Điểm P2' có thể nhập tay hoặc liên kết từ sheet role.</t>
-  </si>
-  <si>
-    <t>STT</t>
-  </si>
-  <si>
-    <t>Điểm P2</t>
-  </si>
-  <si>
-    <t>Rank</t>
-  </si>
-  <si>
-    <t>Ghi chú</t>
-  </si>
-  <si>
-    <t>P2-Core</t>
-  </si>
-  <si>
-    <t>OKR (P2-Delivery)</t>
-  </si>
-  <si>
-    <t>Bùi Văn Hổ</t>
-  </si>
-  <si>
-    <t>Designer, Frontend</t>
-  </si>
-  <si>
-    <t>Nguyễn Huy Hoàng</t>
-  </si>
-  <si>
-    <t>Backend, Frontend</t>
-  </si>
-  <si>
-    <t>Nguyễn Đăng Đức</t>
   </si>
 </sst>
 </file>
@@ -709,7 +709,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -942,11 +942,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1026,10 +1039,52 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1039,88 +1094,59 @@
     <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1475,40 +1501,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
+      <c r="A1" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
     </row>
     <row r="3" spans="1:5" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
+      <c r="A3" s="49" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
     </row>
     <row r="5" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
+      <c r="A5" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
     </row>
     <row r="6" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
+      <c r="A6" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1531,278 +1557,265 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
+      <c r="A1" s="50" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
     </row>
     <row r="3" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="54" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="43"/>
+      <c r="A3" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="55"/>
     </row>
     <row r="4" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="35"/>
+      <c r="A4" s="62" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="52"/>
     </row>
     <row r="5" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="35"/>
+      <c r="A5" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="52"/>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="27"/>
-      <c r="B6" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="35"/>
+      <c r="B6" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="36"/>
+      <c r="D6" s="52"/>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="27"/>
-      <c r="B7" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="35"/>
+      <c r="B7" s="56" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="36"/>
+      <c r="D7" s="52"/>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="27"/>
-      <c r="B8" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="35"/>
+      <c r="B8" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="36"/>
+      <c r="D8" s="52"/>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="28"/>
-      <c r="B9" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="46"/>
+      <c r="B9" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="58"/>
+      <c r="D9" s="59"/>
     </row>
     <row r="11" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="43"/>
+      <c r="A11" s="64" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="55"/>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="27"/>
-      <c r="B12" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="35"/>
+      <c r="B12" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="36"/>
+      <c r="D12" s="52"/>
     </row>
     <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="28"/>
-      <c r="B13" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="46"/>
+      <c r="B13" s="63" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="58"/>
+      <c r="D13" s="59"/>
     </row>
     <row r="16" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="43"/>
+      <c r="A16" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="55"/>
     </row>
     <row r="17" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="35"/>
+      <c r="A17" s="70" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="52"/>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="55" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="46"/>
+      <c r="A18" s="57" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="58"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="59"/>
     </row>
     <row r="19" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="47" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
+      <c r="A19" s="66" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
     </row>
     <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
+      <c r="A20" s="60" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
+      <c r="A21" s="60" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
     </row>
     <row r="23" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
+      <c r="A23" s="71" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
     </row>
     <row r="24" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="42"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="43"/>
+      <c r="A24" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="55"/>
     </row>
     <row r="25" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="27"/>
-      <c r="B25" s="52" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" s="30"/>
-      <c r="D25" s="35"/>
+      <c r="B25" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="36"/>
+      <c r="D25" s="52"/>
     </row>
     <row r="26" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="27"/>
-      <c r="B26" s="52" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="30"/>
-      <c r="D26" s="35"/>
+      <c r="B26" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="36"/>
+      <c r="D26" s="52"/>
     </row>
     <row r="27" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="28"/>
-      <c r="B27" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="46"/>
+      <c r="B27" s="67" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="58"/>
+      <c r="D27" s="59"/>
     </row>
     <row r="29" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="42"/>
-      <c r="C29" s="42"/>
-      <c r="D29" s="43"/>
+      <c r="A29" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="54"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="55"/>
     </row>
     <row r="30" spans="1:4" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="28"/>
-      <c r="B30" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="45"/>
-      <c r="D30" s="46"/>
+      <c r="B30" s="67" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="58"/>
+      <c r="D30" s="59"/>
     </row>
     <row r="32" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="42"/>
-      <c r="C32" s="42"/>
-      <c r="D32" s="43"/>
+      <c r="A32" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="54"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="55"/>
     </row>
     <row r="33" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="27"/>
-      <c r="B33" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="C33" s="30"/>
-      <c r="D33" s="35"/>
+      <c r="B33" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" s="36"/>
+      <c r="D33" s="52"/>
     </row>
     <row r="34" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="28"/>
-      <c r="B34" s="48" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34" s="45"/>
-      <c r="D34" s="46"/>
+      <c r="B34" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="58"/>
+      <c r="D34" s="59"/>
     </row>
     <row r="37" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="B37" s="50"/>
+      <c r="A37" s="68" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="69"/>
     </row>
     <row r="38" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="14" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="15" t="s">
         <v>34</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="15" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="15" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>41</v>
-      </c>
+      <c r="A42" s="15"/>
+      <c r="B42" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="B12:D12"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="A19:D19"/>
@@ -1813,12 +1826,21 @@
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A5:D5"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="B8:D8"/>
-    <mergeCell ref="A20:D20"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B6:D6"/>
@@ -1829,7 +1851,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1840,124 +1862,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
     </row>
     <row r="3" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="60" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="30"/>
+        <v>1</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="36"/>
       <c r="D3" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="60"/>
+        <v>3</v>
+      </c>
+      <c r="E3" s="41"/>
     </row>
     <row r="4" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="60" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="30"/>
+        <v>4</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" s="36"/>
       <c r="D4" s="5" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="E4" s="1"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="B7" s="3">
         <v>35</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="D7" s="3">
-        <f>IF(C7="","",B7*IF(C7="L1",1.5,IF(C7="L2",3.5,IF(C7="L3",5,0)))/100)</f>
-        <v>1.2250000000000001</v>
+        <f>IF(C7="","",B7*IF(C7="L0",0.8,IF(C7="L1",1,IF(C7="L2",1.1,IF(C7="L3",1.2,0))))/100)</f>
+        <v>0.38500000000000001</v>
       </c>
       <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="B8" s="3">
         <v>25</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="D8" s="3">
-        <f>IF(C8="","",B8*IF(C8="L1",1.5,IF(C8="L2",3.5,IF(C8="L3",5,0)))/100)</f>
-        <v>0.875</v>
+        <f>IF(C8="","",B8*IF(C8="L0",0.8,IF(C8="L1",1,IF(C8="L2",1.1,IF(C8="L3",1.2,0))))/100)</f>
+        <v>0.27500000000000002</v>
       </c>
       <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="B9" s="3">
         <v>20</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3" t="str">
-        <f>IF(C9="","",B9*IF(C9="L1",1.5,IF(C9="L2",3.5,IF(C9="L3",5,0)))/100)</f>
-        <v/>
+      <c r="C9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="3">
+        <f>IF(C9="","",B9*IF(C9="L0",0.8,IF(C9="L1",1,IF(C9="L2",1.1,IF(C9="L3",1.2,0))))/100)</f>
+        <v>0.16</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="B10" s="3">
         <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="D10" s="3">
-        <f>IF(C10="","",B10*IF(C10="L1",1.5,IF(C10="L2",3.5,IF(C10="L3",5,0)))/100)</f>
-        <v>0.7</v>
+        <f>IF(C10="","",B10*IF(C10="L0",0.8,IF(C10="L1",1,IF(C10="L2",1.1,IF(C10="L3",1.2,0))))/100)</f>
+        <v>0.22</v>
       </c>
       <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="B11" s="6">
         <v>100</v>
@@ -1965,174 +1989,193 @@
       <c r="C11" s="6"/>
       <c r="D11" s="6">
         <f>SUM(D7:D10)</f>
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="E11" s="7"/>
     </row>
     <row r="13" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="64" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
+      <c r="A13" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="66" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-    </row>
-    <row r="15" spans="1:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="58"/>
+        <v>19</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+    </row>
+    <row r="15" spans="1:5" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="40"/>
     </row>
     <row r="16" spans="1:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="56" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="58"/>
+        <v>23</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="40"/>
     </row>
     <row r="17" spans="1:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="58"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="21"/>
-      <c r="B18" s="22"/>
+        <v>12</v>
+      </c>
+      <c r="B17" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="40"/>
+    </row>
+    <row r="18" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="40"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="21"/>
+      <c r="B19" s="22"/>
     </row>
     <row r="21" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="63" t="s">
-        <v>69</v>
-      </c>
-      <c r="B21" s="57"/>
-      <c r="C21" s="58"/>
+      <c r="A21" s="36"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
     </row>
     <row r="22" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="61" t="s">
-        <v>70</v>
-      </c>
-      <c r="B22" s="57"/>
-      <c r="C22" s="58"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="26"/>
+      <c r="A22" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
+    </row>
+    <row r="23" spans="1:5" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="33"/>
+      <c r="C23" s="34"/>
     </row>
     <row r="24" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" s="15"/>
+      <c r="A24" s="26"/>
+    </row>
+    <row r="25" spans="1:5" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="26" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="E26" s="15"/>
     </row>
     <row r="27" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="B27" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="E27" s="15"/>
+    </row>
+    <row r="28" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E27" s="15"/>
+      <c r="B28" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" s="15"/>
     </row>
     <row r="29" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="65" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29" s="57"/>
-      <c r="C29" s="58"/>
+      <c r="A29" s="36"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="36"/>
     </row>
     <row r="30" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="B30" s="59">
-        <f>IF(COUNTA(C25:C27)=0,"",
-AVERAGE(
- IF(C25="Chưa đạt",1.5,IF(C25="Đạt",3.5,IF(C25="Tốt",5,""))),
- IF(C26="Chưa đạt",1.5,IF(C26="Đạt",3.5,IF(C26="Tốt",5,""))),
- IF(C27="Chưa đạt",1.5,IF(C27="Đạt",3.5,IF(C27="Tốt",5,"")))
-))</f>
-        <v>3.5</v>
-      </c>
-      <c r="C30" s="58"/>
+      <c r="A30" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="39"/>
+      <c r="C30" s="40"/>
     </row>
     <row r="31" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" s="59">
-        <f>IF(OR(D11="",B30=""),"",D11*0.5+B30*0.5)</f>
-        <v>3.15</v>
-      </c>
-      <c r="C31" s="58"/>
+      <c r="A31" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="29">
+        <f>IF((C26&lt;&gt;"")+(C27&lt;&gt;"")+(C28&lt;&gt;"")=0,"",((IF(C26="Chưa đạt",0.8,IF(C26="Đạt",1,IF(C26="Tốt",1.2,0))))+(IF(C27="Chưa đạt",0.8,IF(C27="Đạt",1,IF(C27="Tốt",1.2,0))))+(IF(C28="Chưa đạt",0.8,IF(C28="Đạt",1,IF(C28="Tốt",1.2,0)))))/((C26&lt;&gt;"")+(C27&lt;&gt;"")+(C28&lt;&gt;"")))</f>
+        <v>1</v>
+      </c>
+      <c r="C31" s="30"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="29">
+        <f>IF(OR(D11="",B31=""),"",(D11+B31)/2)</f>
+        <v>1.02</v>
+      </c>
+      <c r="C32" s="30" t="str">
+        <f>IF(B32="","",IF(B32&lt;1,"Chưa đạt",IF(B32&lt;=1,"Đạt",IF(B32&lt;=1.2,"Tốt",""))))</f>
+        <v>Tốt</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B18:E18"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="E3"/>
     <mergeCell ref="A22:C22"/>
@@ -2173,11 +2216,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="C7:C10" xr:uid="{00000000-0002-0000-0200-000000000000}">
-      <formula1>"L1,L2,L3"</formula1>
+    <dataValidation type="list" allowBlank="1" sqref="C25:C28" xr:uid="{00000000-0002-0000-0200-000000000000}">
+      <formula1>"Chưa đạt,Đạt,Tốt"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C25:C27" xr:uid="{00000000-0002-0000-0200-000001000000}">
-      <formula1>"Chưa đạt,Đạt,Tốt"</formula1>
+    <dataValidation type="list" allowBlank="1" sqref="C7:C10" xr:uid="{00000000-0002-0000-0200-000001000000}">
+      <formula1>"L0,L1,L2,L3"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2197,331 +2240,331 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="72" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+    </row>
+    <row r="2" spans="1:4" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-    </row>
-    <row r="2" spans="1:4" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="69" t="s">
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+    </row>
+    <row r="4" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="73" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-    </row>
-    <row r="4" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="68" t="s">
-        <v>83</v>
-      </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
     </row>
     <row r="5" spans="1:4" ht="19.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="8" t="s">
         <v>85</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="79.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="B6" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="D6" s="11" t="s">
         <v>88</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="79.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="B7" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="D7" s="11" t="s">
         <v>91</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="79.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="C8" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="D8" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="79.95" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="C9" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="D9" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="D9" s="11" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="73" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="68" t="s">
-        <v>101</v>
-      </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
     </row>
     <row r="12" spans="1:4" ht="19.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="D12" s="8" t="s">
         <v>85</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="79.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="B13" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="D13" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="79.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="D14" s="11" t="s">
         <v>106</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="79.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B15" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="D15" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="79.95" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B16" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="D16" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="D16" s="11" t="s">
+    </row>
+    <row r="18" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="73" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="68" t="s">
-        <v>114</v>
-      </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
     </row>
     <row r="19" spans="1:4" ht="19.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="D19" s="8" t="s">
         <v>85</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="79.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="D20" s="11" t="s">
         <v>116</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="79.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="B21" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="D21" s="11" t="s">
         <v>119</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="79.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B22" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="D22" s="11" t="s">
         <v>122</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="79.95" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B23" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="D23" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="D23" s="11" t="s">
+    </row>
+    <row r="25" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="73" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="68" t="s">
-        <v>127</v>
-      </c>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
     </row>
     <row r="26" spans="1:4" ht="19.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="B26" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="D26" s="8" t="s">
         <v>85</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="79.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="B27" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="D27" s="11" t="s">
         <v>129</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="79.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="B28" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C28" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="D28" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="79.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B29" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="D29" s="11" t="s">
         <v>135</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="79.95" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B30" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="D30" s="11" t="s">
         <v>138</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2560,71 +2603,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="60" t="s">
-        <v>141</v>
-      </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
     </row>
     <row r="5" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="J5" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="J5" s="12" t="s">
-        <v>147</v>
-      </c>
       <c r="K5" s="12" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L5" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="M5" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="M5" s="16" t="s">
-        <v>147</v>
-      </c>
       <c r="N5" s="16" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -2632,10 +2675,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>148</v>
+        <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -2658,11 +2701,11 @@
       </c>
       <c r="M6" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N6" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -2670,10 +2713,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -2696,11 +2739,11 @@
       </c>
       <c r="M7" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N7" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -2708,10 +2751,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -2734,11 +2777,11 @@
       </c>
       <c r="M8" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N8" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -2746,10 +2789,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -2772,11 +2815,11 @@
       </c>
       <c r="M9" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N9" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -2806,11 +2849,11 @@
       </c>
       <c r="M10" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N10" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -2840,11 +2883,11 @@
       </c>
       <c r="M11" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N11" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -2874,11 +2917,11 @@
       </c>
       <c r="M12" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N12" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -2908,11 +2951,11 @@
       </c>
       <c r="M13" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N13" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -2942,11 +2985,11 @@
       </c>
       <c r="M14" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N14" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -2976,11 +3019,11 @@
       </c>
       <c r="M15" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N15" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -3010,11 +3053,11 @@
       </c>
       <c r="M16" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N16" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -3044,11 +3087,11 @@
       </c>
       <c r="M17" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N17" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -3078,11 +3121,11 @@
       </c>
       <c r="M18" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N18" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -3112,11 +3155,11 @@
       </c>
       <c r="M19" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N19" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -3146,11 +3189,11 @@
       </c>
       <c r="M20" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N20" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -3180,11 +3223,11 @@
       </c>
       <c r="M21" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N21" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -3214,11 +3257,11 @@
       </c>
       <c r="M22" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -3248,11 +3291,11 @@
       </c>
       <c r="M23" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N23" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -3282,11 +3325,11 @@
       </c>
       <c r="M24" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N24" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -3316,11 +3359,11 @@
       </c>
       <c r="M25" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N25" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -3350,11 +3393,11 @@
       </c>
       <c r="M26" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N26" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -3384,11 +3427,11 @@
       </c>
       <c r="M27" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N27" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -3418,11 +3461,11 @@
       </c>
       <c r="M28" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N28" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -3452,11 +3495,11 @@
       </c>
       <c r="M29" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N29" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -3486,11 +3529,11 @@
       </c>
       <c r="M30" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N30" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -3520,11 +3563,11 @@
       </c>
       <c r="M31" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N31" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -3554,11 +3597,11 @@
       </c>
       <c r="M32" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N32" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
@@ -3588,11 +3631,11 @@
       </c>
       <c r="M33" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N33" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -3622,11 +3665,11 @@
       </c>
       <c r="M34" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N34" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
@@ -3656,11 +3699,11 @@
       </c>
       <c r="M35" s="13">
         <f>Product_Engineer!B30</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N35" s="13">
         <f>Product_Engineer!B31</f>
-        <v>3.15</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
